--- a/code_mapping/[공통] 4. 계정코드매핑정의서.xlsx
+++ b/code_mapping/[공통] 4. 계정코드매핑정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="계정코드매핑정의서" sheetId="7" r:id="rId1"/>
@@ -139,7 +139,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20260513</t>
+    <t>20260903</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2364,7 +2364,7 @@
       <c r="H141" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="pO+8cq16UzyZLqRYzVJah88aVutUpMhyx94bQIL3Tinptk4In2e9s+jY5kYlbB7gvexkypr0uxl8aaYpFwaPvg==" saltValue="LAzwq1G74JTnILC0SvW38A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B3:H4"/>
   </mergeCells>
@@ -2553,7 +2553,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="h8hlCACN838vcbJ8LfOhD58904ELgVrlfacUe5ZwgrgZfX06VGGCpdc2qx1PQzJgAWqmea1x6Af7IkTO2eeC3Q==" saltValue="i/znXm6/wnVxLf89m+of9w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:H3"/>
   </mergeCells>
